--- a/kobo/gestores_diagnostico_completo.xlsx
+++ b/kobo/gestores_diagnostico_completo.xlsx
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Q1.1r. Infraestrutura da rede — em quantas escolas da rede existe cada espaço?</t>
+          <t>Q1.1. Infraestrutura da rede — em quantas escolas da rede existe cada espaço?</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>

--- a/kobo/gestores_diagnostico_completo.xlsx
+++ b/kobo/gestores_diagnostico_completo.xlsx
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Água, esgoto e resíduos — local</t>
+          <t>Água, esgoto e resíduos — escola</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Responda com base na sua visão geral das locais da rede/região de atuação. Estimativas são bem-vindas; "Não sabe" é uma resposta válida e vira lacuna de conhecimento registrada.</t>
+          <t>Responda com base na sua visão geral das escolas da rede/região de atuação. Estimativas são bem-vindas; "Não sabe" é uma resposta válida e vira lacuna de conhecimento registrada.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>

--- a/kobo/gestores_diagnostico_completo.xlsx
+++ b/kobo/gestores_diagnostico_completo.xlsx
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Q1.15. Em que espaços do local esses alagamentos costumam ocorrer (Ex: apenas na área externa, invadem as salas, etc)?</t>
+          <t>Q1.15. Em que espaços da escola esses alagamentos costumam ocorrer (Ex: apenas na área externa, invadem as salas, etc)?</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>

--- a/kobo/gestores_diagnostico_completo.xlsx
+++ b/kobo/gestores_diagnostico_completo.xlsx
@@ -13828,7 +13828,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir.</t>
+          <t>Obrigado(a) pela sua participação! Suas respostas ajudam a construir um diagnóstico mais completo. Revise o que respondeu, confirme abaixo e clique em Enviar para concluir. ATENÇÃO: depois de clicar em Enviar, aparecerá a mensagem "Submission successful" e o formulário voltará em branco. Isso significa que suas respostas FORAM ENVIADAS. Não preencha nem envie novamente.</t>
         </is>
       </c>
       <c r="D508" t="inlineStr"/>

--- a/kobo/gestores_diagnostico_completo.xlsx
+++ b/kobo/gestores_diagnostico_completo.xlsx
@@ -5039,8 +5039,16 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
@@ -5143,8 +5151,16 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -5983,8 +5999,16 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -6095,8 +6119,16 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J209" t="inlineStr"/>
     </row>
     <row r="210">
@@ -6935,8 +6967,16 @@
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>not(selected(., 'nao_sabe') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>"Não sabe" não pode ser combinado com outras opções.</t>
+        </is>
+      </c>
       <c r="J241" t="inlineStr"/>
     </row>
     <row r="242">
@@ -14658,7 +14698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C676"/>
+  <dimension ref="A1:C681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18472,17 +18512,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>areas_curr</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>disciplinas_separadas</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Disciplinas separadas</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -18494,12 +18534,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>mesmo_tema_sem_planejamento_conj</t>
+          <t>disciplinas_separadas</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Mesmo tema, sem planejamento conjunto</t>
+          <t>Disciplinas separadas</t>
         </is>
       </c>
     </row>
@@ -18511,12 +18551,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>algum_planejamento_conjunto</t>
+          <t>mesmo_tema_sem_planejamento_conj</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Algum planejamento conjunto</t>
+          <t>Mesmo tema, sem planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -18528,12 +18568,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>investigacao_conjunta</t>
+          <t>algum_planejamento_conjunto</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Investigação conjunta</t>
+          <t>Algum planejamento conjunto</t>
         </is>
       </c>
     </row>
@@ -18545,12 +18585,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>objetivos_comuns</t>
+          <t>investigacao_conjunta</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Objetivos comuns</t>
+          <t>Investigação conjunta</t>
         </is>
       </c>
     </row>
@@ -18562,12 +18602,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>intervencao_territorial_coletiva</t>
+          <t>objetivos_comuns</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Intervenção territorial coletiva</t>
+          <t>Objetivos comuns</t>
         </is>
       </c>
     </row>
@@ -18579,12 +18619,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>sem_articulacao</t>
+          <t>intervencao_territorial_coletiva</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Sem articulação</t>
+          <t>Intervenção territorial coletiva</t>
         </is>
       </c>
     </row>
@@ -18596,29 +18636,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>sem_articulacao</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Sem articulação</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>freq_ea</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>diaria</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Diária</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -18630,12 +18670,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>diaria</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Diária</t>
         </is>
       </c>
     </row>
@@ -18647,12 +18687,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>semanal</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Semanal</t>
         </is>
       </c>
     </row>
@@ -18664,12 +18704,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>esporadica</t>
+          <t>mensal</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Esporádica</t>
+          <t>Mensal</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18721,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>esporadica</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Esporádica</t>
         </is>
       </c>
     </row>
@@ -18698,12 +18738,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>nao_ocorre</t>
+          <t>anual</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Não ocorre</t>
+          <t>Anual</t>
         </is>
       </c>
     </row>
@@ -18715,29 +18755,29 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nao_ocorre</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Não ocorre</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>contexto_ea</t>
+          <t>freq_ea</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>sala_de_aula</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Sala de aula</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -18749,12 +18789,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>patio_area_externa</t>
+          <t>sala_de_aula</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Pátio/área externa</t>
+          <t>Sala de aula</t>
         </is>
       </c>
     </row>
@@ -18766,12 +18806,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>visita_de_campo</t>
+          <t>patio_area_externa</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Visita de campo</t>
+          <t>Pátio/área externa</t>
         </is>
       </c>
     </row>
@@ -18783,12 +18823,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>projeto_especial</t>
+          <t>visita_de_campo</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Projeto especial</t>
+          <t>Visita de campo</t>
         </is>
       </c>
     </row>
@@ -18800,12 +18840,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>feira</t>
+          <t>projeto_especial</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Feira</t>
+          <t>Projeto especial</t>
         </is>
       </c>
     </row>
@@ -18817,46 +18857,46 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>feira</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Feira</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>professor_individualmente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Professor(a) individualmente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>quem_planejou</t>
+          <t>contexto_ea</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>grupo_de_professores</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Grupo de professores(as)</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -18868,12 +18908,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>coordenacao_pedagogica</t>
+          <t>professor_individualmente</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Coordenação pedagógica</t>
+          <t>Professor(a) individualmente</t>
         </is>
       </c>
     </row>
@@ -18885,12 +18925,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>grupo_de_professores</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Grupo de professores(as)</t>
         </is>
       </c>
     </row>
@@ -18902,12 +18942,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>coordenacao_pedagogica</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Coordenação pedagógica</t>
         </is>
       </c>
     </row>
@@ -18919,46 +18959,46 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>papel_estud</t>
+          <t>quem_planejou</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>participante_pontual</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Participante pontual</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -18970,12 +19010,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
@@ -18987,12 +19027,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>participante_pontual</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Participante pontual</t>
         </is>
       </c>
     </row>
@@ -19004,46 +19044,46 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>depende_da_permanencia_de_profes</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Depende da permanência de professor(a) específico(a)</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>continuidade_ativ</t>
+          <t>papel_estud</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Tem continuidade institucional garantida</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19055,12 +19095,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>depende_da_permanencia_de_profes</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Depende da permanência de professor(a) específico(a)</t>
         </is>
       </c>
     </row>
@@ -19072,46 +19112,46 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Tem continuidade institucional garantida</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>freq5</t>
+          <t>continuidade_ativ</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>raramente</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Raramente</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19123,12 +19163,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>as_vezes</t>
+          <t>nunca</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Nunca</t>
         </is>
       </c>
     </row>
@@ -19140,12 +19180,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>frequentemente</t>
+          <t>raramente</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Frequentemente</t>
+          <t>Raramente</t>
         </is>
       </c>
     </row>
@@ -19157,46 +19197,46 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>as_vezes</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Às vezes</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>agua</t>
+          <t>frequentemente</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>Frequentemente</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>temas</t>
+          <t>freq5</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>biodiversidade</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Biodiversidade</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19208,12 +19248,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>residuos</t>
+          <t>agua</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Resíduos</t>
+          <t>Água</t>
         </is>
       </c>
     </row>
@@ -19225,12 +19265,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>mudancas_climaticas</t>
+          <t>biodiversidade</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Mudanças climáticas</t>
+          <t>Biodiversidade</t>
         </is>
       </c>
     </row>
@@ -19242,12 +19282,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>energia</t>
+          <t>residuos</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Energia</t>
+          <t>Resíduos</t>
         </is>
       </c>
     </row>
@@ -19259,12 +19299,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>alimentacao</t>
+          <t>mudancas_climaticas</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Alimentação</t>
+          <t>Mudanças climáticas</t>
         </is>
       </c>
     </row>
@@ -19276,12 +19316,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>consumo</t>
+          <t>energia</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Energia</t>
         </is>
       </c>
     </row>
@@ -19293,12 +19333,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>saneamento</t>
+          <t>alimentacao</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Alimentação</t>
         </is>
       </c>
     </row>
@@ -19310,12 +19350,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>saude</t>
+          <t>consumo</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Consumo</t>
         </is>
       </c>
     </row>
@@ -19327,12 +19367,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>riscos_desastres</t>
+          <t>saneamento</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Riscos/desastres</t>
+          <t>Saneamento</t>
         </is>
       </c>
     </row>
@@ -19344,12 +19384,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>justica_socioambiental</t>
+          <t>saude</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Justiça socioambiental</t>
+          <t>Saúde</t>
         </is>
       </c>
     </row>
@@ -19361,12 +19401,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>riscos_desastres</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Riscos/desastres</t>
         </is>
       </c>
     </row>
@@ -19378,12 +19418,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>conflitos</t>
+          <t>justica_socioambiental</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Conflitos</t>
+          <t>Justiça socioambiental</t>
         </is>
       </c>
     </row>
@@ -19395,12 +19435,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>povos_e_comunidades_tradicionais</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Povos e comunidades tradicionais</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
@@ -19412,63 +19452,63 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conflitos</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Conflitos</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>falta_de_formacao</t>
+          <t>povos_e_comunidades_tradicionais</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Falta de formação</t>
+          <t>Povos e comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>falta_de_material</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Falta de material</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>causa_dif</t>
+          <t>temas</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>tema_sensivel_delicado</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Tema sensível/delicado</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19480,12 +19520,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>falta_de_formacao</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Falta de formação</t>
         </is>
       </c>
     </row>
@@ -19497,12 +19537,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>curriculo</t>
+          <t>falta_de_material</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Currículo</t>
+          <t>Falta de material</t>
         </is>
       </c>
     </row>
@@ -19514,63 +19554,63 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tema_sensivel_delicado</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tema sensível/delicado</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>aula_expositiva</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Aula expositiva</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>projeto</t>
+          <t>curriculo</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Currículo</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>causa_dif</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>oficina</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Oficina</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -19582,12 +19622,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>saida_de_campo</t>
+          <t>aula_expositiva</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Saída de campo</t>
+          <t>Aula expositiva</t>
         </is>
       </c>
     </row>
@@ -19599,12 +19639,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>horta_experimentacao</t>
+          <t>projeto</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Horta/experimentação</t>
+          <t>Projeto</t>
         </is>
       </c>
     </row>
@@ -19616,12 +19656,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>rodas_de_conversa</t>
+          <t>oficina</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Rodas de conversa</t>
+          <t>Oficina</t>
         </is>
       </c>
     </row>
@@ -19633,12 +19673,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>producao_audiovisual</t>
+          <t>saida_de_campo</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Produção audiovisual</t>
+          <t>Saída de campo</t>
         </is>
       </c>
     </row>
@@ -19650,12 +19690,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>cartografia</t>
+          <t>horta_experimentacao</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Cartografia</t>
+          <t>Horta/experimentação</t>
         </is>
       </c>
     </row>
@@ -19667,80 +19707,80 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>rodas_de_conversa</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Rodas de conversa</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>producao_audiovisual</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Produção audiovisual</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>pouco</t>
+          <t>cartografia</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Pouco</t>
+          <t>Cartografia</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>impacto_form</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>significativo</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Significativo</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19752,80 +19792,80 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>pouco</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>1 — Nada confiante(a)</t>
+          <t>Pouco</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2 — Pouco confiante</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>significativo</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3 — Moderadamente confiante</t>
+          <t>Significativo</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>confianca</t>
+          <t>impacto_form</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>4 — Confiante</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -19837,12 +19877,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>5 — Muito confiante</t>
+          <t>1 — Nada confiante(a)</t>
         </is>
       </c>
     </row>
@@ -19854,80 +19894,80 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>2 — Pouco confiante</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>3 — Moderadamente confiante</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>material_didatico</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Material didático</t>
+          <t>4 — Confiante</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>tempo_de_planejamento</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Tempo de planejamento</t>
+          <t>5 — Muito confiante</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>apoio</t>
+          <t>confianca</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -19939,12 +19979,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>parcerias</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Parcerias</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -19956,12 +19996,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>material_didatico</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Material didático</t>
         </is>
       </c>
     </row>
@@ -19973,80 +20013,80 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tempo_de_planejamento</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Tempo de planejamento</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>curriculo_sobrecarregado</t>
+          <t>parcerias</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Currículo sobrecarregado</t>
+          <t>Parcerias</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>formacao</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Formação</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>barreiras</t>
+          <t>apoio</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Materiais</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20058,12 +20098,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
@@ -20075,12 +20115,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>apoio_da_gestao</t>
+          <t>curriculo_sobrecarregado</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Apoio da gestão</t>
+          <t>Currículo sobrecarregado</t>
         </is>
       </c>
     </row>
@@ -20092,12 +20132,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>planejamento_coletivo</t>
+          <t>formacao</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Planejamento coletivo</t>
+          <t>Formação</t>
         </is>
       </c>
     </row>
@@ -20109,12 +20149,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>interdisciplinaridade</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Interdisciplinaridade</t>
+          <t>Materiais</t>
         </is>
       </c>
     </row>
@@ -20126,12 +20166,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>informacoes_territoriais</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Informações territoriais</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
@@ -20143,12 +20183,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>descontinuidade</t>
+          <t>apoio_da_gestao</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Descontinuidade</t>
+          <t>Apoio da gestão</t>
         </is>
       </c>
     </row>
@@ -20160,12 +20200,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>rotatividade_de_profissionais</t>
+          <t>planejamento_coletivo</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Rotatividade de profissionais</t>
+          <t>Planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -20177,148 +20217,148 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>interdisciplinaridade</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Interdisciplinaridade</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>informacoes_territoriais</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Informações territoriais</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>descontinuidade</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Descontinuidade</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>rotatividade_de_profissionais</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Rotatividade de profissionais</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>intensidade</t>
+          <t>barreiras</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>nao_se_aplica</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Outras</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>reserva_tempo_para_planejamento_</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Reserva tempo para planejamento coletivo</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>inclui_a_ea_no_ppp_planejamento_</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Inclui a EA no PPP/planejamento anual</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>viabiliza_recursos_e_materiais</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Viabiliza recursos e materiais</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>apoio_gestao</t>
+          <t>intensidade</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>articula_parcerias_externas</t>
+          <t>nao_se_aplica</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Articula parcerias externas</t>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -20330,12 +20370,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>apoia_projetos_de_estudantes</t>
+          <t>reserva_tempo_para_planejamento_</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Apoia projetos de estudantes</t>
+          <t>Reserva tempo para planejamento coletivo</t>
         </is>
       </c>
     </row>
@@ -20347,12 +20387,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>participa_de_formacoes_sobre_o_t</t>
+          <t>inclui_a_ea_no_ppp_planejamento_</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Participa de formações sobre o tema</t>
+          <t>Inclui a EA no PPP/planejamento anual</t>
         </is>
       </c>
     </row>
@@ -20364,12 +20404,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>acompanha_e_valoriza_as_praticas</t>
+          <t>viabiliza_recursos_e_materiais</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Acompanha e valoriza as práticas da equipe</t>
+          <t>Viabiliza recursos e materiais</t>
         </is>
       </c>
     </row>
@@ -20381,12 +20421,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>articula_parcerias_externas</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Nenhum apoio sistemático</t>
+          <t>Articula parcerias externas</t>
         </is>
       </c>
     </row>
@@ -20398,80 +20438,80 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>apoia_projetos_de_estudantes</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Apoia projetos de estudantes</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>participa_de_formacoes_sobre_o_t</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Participa de formações sobre o tema</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>apm_caixa_escolar</t>
+          <t>acompanha_e_valoriza_as_praticas</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>APM / caixa escolar</t>
+          <t>Acompanha e valoriza as práticas da equipe</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Nenhum apoio sistemático</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>instancias</t>
+          <t>apoio_gestao</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>conselho_de_classe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Conselho de classe</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -20483,12 +20523,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>reuniao_pedagogica_planejamento_</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Reunião pedagógica/planejamento coletivo</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
@@ -20500,12 +20540,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>associacao_de_pais_e_mestres</t>
+          <t>apm_caixa_escolar</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Associação de pais e mestres</t>
+          <t>APM / caixa escolar</t>
         </is>
       </c>
     </row>
@@ -20517,12 +20557,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
@@ -20534,80 +20574,80 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>conselho_de_classe</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Conselho de classe</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>livros_didaticos</t>
+          <t>reuniao_pedagogica_planejamento_</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Livros didáticos</t>
+          <t>Reunião pedagógica/planejamento coletivo</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>associacao_de_pais_e_mestres</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Vídeos</t>
+          <t>Associação de pais e mestres</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>jogos</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Jogos</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>materiais</t>
+          <t>instancias</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>kits_cientificos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Kits científicos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -20619,12 +20659,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>materiais_produzidos_pela_escola</t>
+          <t>livros_didaticos</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Materiais produzidos pelo local</t>
+          <t>Livros didáticos</t>
         </is>
       </c>
     </row>
@@ -20636,12 +20676,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>recursos_digitais</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Recursos digitais</t>
+          <t>Vídeos</t>
         </is>
       </c>
     </row>
@@ -20653,87 +20693,87 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>jogos</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Jogos</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>facil</t>
+          <t>kits_cientificos</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Fácil</t>
+          <t>Kits científicos</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>materiais_produzidos_pela_escola</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Materiais produzidos pelo local</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>dificil</t>
+          <t>recursos_digitais</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Difícil</t>
+          <t>Recursos digitais</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>acesso_mat</t>
+          <t>materiais</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -20750,75 +20790,75 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>espectadores</t>
+          <t>facil</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Espectadores</t>
+          <t>Fácil</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>colaboradores_pontuais</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Colaboradores pontuais</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>protagonistas_em_alguns_momentos</t>
+          <t>dificil</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Protagonistas em alguns momentos</t>
+          <t>Difícil</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>protagonistas_continuos</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Protagonistas contínuos</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>part_estud</t>
+          <t>acesso_mat</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -20835,153 +20875,153 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>garantida_institucionalmente</t>
+          <t>espectadores</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Garantida institucionalmente</t>
+          <t>Espectadores</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>dependente_de_pessoas_especifica</t>
+          <t>colaboradores_pontuais</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Dependente de pessoas específicas</t>
+          <t>Colaboradores pontuais</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>protagonistas_em_alguns_momentos</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Protagonistas em alguns momentos</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>continuidade_proj</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>protagonistas_continuos</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Protagonistas contínuos</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>part_estud</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>garantida_institucionalmente</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Garantida institucionalmente</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>dependente_de_pessoas_especifica</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Dependente de pessoas específicas</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>quem_part</t>
+          <t>continuidade_proj</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -20993,12 +21033,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -21010,12 +21050,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>instituicao_parceira</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Instituição parceira</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -21027,182 +21067,182 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>informativa</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Informativa (recebem informação)</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>consultiva</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Consultiva (são ouvidos)</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>colaborativa</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Colaborativa (constroem junto)</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>instituicao_parceira</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Protagonista (decidem e conduzem)</t>
+          <t>Instituição parceira</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>nivel_part</t>
+          <t>quem_part</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>gremio_estudantil</t>
+          <t>informativa</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Grêmio estudantil</t>
+          <t>Informativa (recebem informação)</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>assembleias</t>
+          <t>consultiva</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Assembleias</t>
+          <t>Consultiva (são ouvidos)</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>projetos_protagonizados_por_estu</t>
+          <t>colaborativa</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Projetos protagonizados por estudantes</t>
+          <t>Colaborativa (constroem junto)</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>conselhos</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Conselhos</t>
+          <t>Protagonista (decidem e conduzem)</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>esp_estud</t>
+          <t>nivel_part</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -21214,267 +21254,267 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>gremio_estudantil</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Grêmio estudantil</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>ausente</t>
+          <t>assembleias</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Ausente</t>
+          <t>Assembleias</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>esporadico</t>
+          <t>projetos_protagonizados_por_estu</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Esporádico</t>
+          <t>Projetos protagonizados por estudantes</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>conselhos</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Conselhos</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ativo_protagonista</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Ativo/protagonista</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>env_fam</t>
+          <t>esp_estud</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>horario_de_trabalho</t>
+          <t>ausente</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Horário de trabalho</t>
+          <t>Ausente</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>distancia</t>
+          <t>esporadico</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Distância</t>
+          <t>Esporádico</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>comunicacao_inadequada</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Comunicação inadequada</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>falta_de_convite_convocacao</t>
+          <t>ativo_protagonista</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Falta de convite/convocação</t>
+          <t>Ativo/protagonista</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>barr_fam</t>
+          <t>env_fam</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>sec_educacao</t>
+          <t>horario_de_trabalho</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Secretaria de Educação</t>
+          <t>Horário de trabalho</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>sec_meio_amb</t>
+          <t>distancia</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Secretaria de Meio Ambiente</t>
+          <t>Distância</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>comunicacao_inadequada</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Comunicação inadequada</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>sec_saude</t>
+          <t>falta_de_convite_convocacao</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Secretaria de Saúde</t>
+          <t>Falta de convite/convocação</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>cat_ator</t>
+          <t>barr_fam</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>assist_social</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Assistência Social</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -21486,12 +21526,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>obras</t>
+          <t>sec_educacao</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Obras</t>
+          <t>Secretaria de Educação</t>
         </is>
       </c>
     </row>
@@ -21503,12 +21543,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>bombeiros</t>
+          <t>sec_meio_amb</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Bombeiros</t>
+          <t>Secretaria de Meio Ambiente</t>
         </is>
       </c>
     </row>
@@ -21520,12 +21560,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>ubs</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -21537,12 +21577,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>vigilancia</t>
+          <t>sec_saude</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Vigilância</t>
+          <t>Secretaria de Saúde</t>
         </is>
       </c>
     </row>
@@ -21554,12 +21594,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>outro_publico</t>
+          <t>assist_social</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Outro (poder público)</t>
+          <t>Assistência Social</t>
         </is>
       </c>
     </row>
@@ -21571,12 +21611,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>obras</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Obras</t>
         </is>
       </c>
     </row>
@@ -21588,12 +21628,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>inst_federal</t>
+          <t>bombeiros</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Instituto Federal</t>
+          <t>Bombeiros</t>
         </is>
       </c>
     </row>
@@ -21605,12 +21645,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>escola_tecnica</t>
+          <t>ubs</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Escola técnica</t>
+          <t>UBS</t>
         </is>
       </c>
     </row>
@@ -21622,12 +21662,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>centro_pesquisa</t>
+          <t>vigilancia</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Centro de pesquisa</t>
+          <t>Vigilância</t>
         </is>
       </c>
     </row>
@@ -21639,12 +21679,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>museu</t>
+          <t>outro_publico</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Museu</t>
+          <t>Outro (poder público)</t>
         </is>
       </c>
     </row>
@@ -21656,12 +21696,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>jardim_botanico</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Jardim botânico</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
@@ -21673,12 +21713,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>outro_educ_ciencia</t>
+          <t>inst_federal</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Outro (educação/ciência)</t>
+          <t>Instituto Federal</t>
         </is>
       </c>
     </row>
@@ -21690,12 +21730,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>assoc_moradores</t>
+          <t>escola_tecnica</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Associação de moradores</t>
+          <t>Escola técnica</t>
         </is>
       </c>
     </row>
@@ -21707,12 +21747,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>centro_pesquisa</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Centro de pesquisa</t>
         </is>
       </c>
     </row>
@@ -21724,12 +21764,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>cooperativa</t>
+          <t>museu</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Cooperativa</t>
+          <t>Museu</t>
         </is>
       </c>
     </row>
@@ -21741,12 +21781,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>catadores</t>
+          <t>jardim_botanico</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Catadores</t>
+          <t>Jardim botânico</t>
         </is>
       </c>
     </row>
@@ -21758,12 +21798,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>mov_sociais</t>
+          <t>outro_educ_ciencia</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Movimentos sociais</t>
+          <t>Outro (educação/ciência)</t>
         </is>
       </c>
     </row>
@@ -21775,12 +21815,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>coletivos</t>
+          <t>assoc_moradores</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Coletivos</t>
+          <t>Associação de moradores</t>
         </is>
       </c>
     </row>
@@ -21792,12 +21832,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>grupos_culturais</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Grupos culturais</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
@@ -21809,12 +21849,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>org_comunit_relig</t>
+          <t>cooperativa</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Organizações comunitárias/religiosas</t>
+          <t>Cooperativa</t>
         </is>
       </c>
     </row>
@@ -21826,12 +21866,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>outro_soc_civil</t>
+          <t>catadores</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Outro (sociedade civil)</t>
+          <t>Catadores</t>
         </is>
       </c>
     </row>
@@ -21843,12 +21883,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>povos_indigenas</t>
+          <t>mov_sociais</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Povos indígenas</t>
+          <t>Movimentos sociais</t>
         </is>
       </c>
     </row>
@@ -21860,12 +21900,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>quilombolas</t>
+          <t>coletivos</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Quilombolas</t>
+          <t>Coletivos</t>
         </is>
       </c>
     </row>
@@ -21877,12 +21917,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>agric_familiares</t>
+          <t>grupos_culturais</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Agricultores familiares</t>
+          <t>Grupos culturais</t>
         </is>
       </c>
     </row>
@@ -21894,12 +21934,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>pescadores</t>
+          <t>org_comunit_relig</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Pescadores</t>
+          <t>Organizações comunitárias/religiosas</t>
         </is>
       </c>
     </row>
@@ -21911,12 +21951,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>com_tradicionais</t>
+          <t>outro_soc_civil</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Comunidades tradicionais</t>
+          <t>Outro (sociedade civil)</t>
         </is>
       </c>
     </row>
@@ -21928,12 +21968,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>liderancas</t>
+          <t>povos_indigenas</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Lideranças</t>
+          <t>Povos indígenas</t>
         </is>
       </c>
     </row>
@@ -21945,12 +21985,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>detentores_saberes</t>
+          <t>quilombolas</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Detentores de conhecimentos locais</t>
+          <t>Quilombolas</t>
         </is>
       </c>
     </row>
@@ -21962,97 +22002,97 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>outro_comunidades</t>
+          <t>agric_familiares</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Outro (comunidades e conhecimentos)</t>
+          <t>Agricultores familiares</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>nao_existe</t>
+          <t>pescadores</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Não existe no território</t>
+          <t>Pescadores</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>nao_sei</t>
+          <t>com_tradicionais</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Não sei se existe</t>
+          <t>Comunidades tradicionais</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>sem_contato</t>
+          <t>liderancas</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Existe, mas nunca houve contato</t>
+          <t>Lideranças</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>contato_pontual</t>
+          <t>detentores_saberes</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
+          <t>Detentores de conhecimentos locais</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>nivel_rel_grade</t>
+          <t>cat_ator</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>parceria</t>
+          <t>outro_comunidades</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Parceria — já colaboram em ações combinadas</t>
+          <t>Outro (comunidades e conhecimentos)</t>
         </is>
       </c>
     </row>
@@ -22064,97 +22104,97 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>nao_existe</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Articulação permanente — parceria contínua e estruturada</t>
+          <t>Não existe no território</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>nao_sei</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Não sei se existe</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>comunicados_impressos</t>
+          <t>sem_contato</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Comunicados impressos</t>
+          <t>Existe, mas nunca houve contato</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>reunioes</t>
+          <t>contato_pontual</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Contato pontual, sem combinação formal (ainda não é parceiro(a))</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>parceria</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Parceria — já colaboram em ações combinadas</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>canais</t>
+          <t>nivel_rel_grade</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>alto_falante_radio_local</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Alto-falante/rádio local</t>
+          <t>Articulação permanente — parceria contínua e estruturada</t>
         </is>
       </c>
     </row>
@@ -22166,250 +22206,250 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>comunicados_impressos</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Comunicados impressos</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>parcialmente</t>
+          <t>reunioes</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Parcialmente</t>
+          <t>Reuniões</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>suficiente</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>alto_falante_radio_local</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Alto-falante/rádio local</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>canais</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>falta_de_contato</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Falta de contato</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>burocracia</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Burocracia</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>desconfianca_historico_de_relaca</t>
+          <t>parcialmente</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Desconfiança/histórico de relação</t>
+          <t>Parcialmente</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>falta_de_tempo</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Falta de tempo</t>
+          <t>Não</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>barr_artic</t>
+          <t>suficiente</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>enchente</t>
+          <t>falta_de_contato</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Enchente</t>
+          <t>Falta de contato</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>inundacao</t>
+          <t>burocracia</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Inundação</t>
+          <t>Burocracia</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>alagamento</t>
+          <t>desconfianca_historico_de_relaca</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Alagamento</t>
+          <t>Desconfiança/histórico de relação</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>enxurrada</t>
+          <t>falta_de_tempo</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Enxurrada</t>
+          <t>Falta de tempo</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ameacas</t>
+          <t>barr_artic</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>deslizamento</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Deslizamento</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -22421,12 +22461,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>erosao</t>
+          <t>enchente</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Erosão</t>
+          <t>Enchente</t>
         </is>
       </c>
     </row>
@@ -22438,12 +22478,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>estiagem_seca</t>
+          <t>inundacao</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Estiagem/seca</t>
+          <t>Inundação</t>
         </is>
       </c>
     </row>
@@ -22455,12 +22495,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>falta_de_agua</t>
+          <t>alagamento</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Falta de água</t>
+          <t>Alagamento</t>
         </is>
       </c>
     </row>
@@ -22472,12 +22512,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>onda_de_calor</t>
+          <t>enxurrada</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Onda de calor</t>
+          <t>Enxurrada</t>
         </is>
       </c>
     </row>
@@ -22489,12 +22529,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>frio_intenso</t>
+          <t>deslizamento</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Frio intenso</t>
+          <t>Deslizamento</t>
         </is>
       </c>
     </row>
@@ -22506,12 +22546,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>tempestades</t>
+          <t>erosao</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Tempestades</t>
+          <t>Erosão</t>
         </is>
       </c>
     </row>
@@ -22523,12 +22563,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>vendavais</t>
+          <t>estiagem_seca</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Vendavais</t>
+          <t>Estiagem/seca</t>
         </is>
       </c>
     </row>
@@ -22540,12 +22580,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>granizo</t>
+          <t>falta_de_agua</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Granizo</t>
+          <t>Falta de água</t>
         </is>
       </c>
     </row>
@@ -22557,12 +22597,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>ciclones</t>
+          <t>onda_de_calor</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Ciclones</t>
+          <t>Onda de calor</t>
         </is>
       </c>
     </row>
@@ -22574,12 +22614,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>queimadas</t>
+          <t>frio_intenso</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Queimadas</t>
+          <t>Frio intenso</t>
         </is>
       </c>
     </row>
@@ -22591,12 +22631,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>incendios</t>
+          <t>tempestades</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Incêndios</t>
+          <t>Tempestades</t>
         </is>
       </c>
     </row>
@@ -22608,12 +22648,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>fumaca_poluicao_atmosferica</t>
+          <t>vendavais</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Fumaça/poluição atmosférica</t>
+          <t>Vendavais</t>
         </is>
       </c>
     </row>
@@ -22625,12 +22665,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>contaminacao_da_agua</t>
+          <t>granizo</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Contaminação da água</t>
+          <t>Granizo</t>
         </is>
       </c>
     </row>
@@ -22642,12 +22682,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>problemas_relacionados_a_residuo</t>
+          <t>ciclones</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Problemas relacionados a resíduos</t>
+          <t>Ciclones</t>
         </is>
       </c>
     </row>
@@ -22659,182 +22699,182 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>queimadas</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Queimadas</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>observacao_ao_longo_dos_anos</t>
+          <t>incendios</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Observação ao longo dos anos</t>
+          <t>Incêndios</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>relatos_de_moradores_antigos</t>
+          <t>fumaca_poluicao_atmosferica</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Relatos de moradores antigos</t>
+          <t>Fumaça/poluição atmosférica</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>comparacao_com_registros</t>
+          <t>contaminacao_da_agua</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Comparação com registros</t>
+          <t>Contaminação da água</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>noticias</t>
+          <t>problemas_relacionados_a_residuo</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Notícias</t>
+          <t>Problemas relacionados a resíduos</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>base_percepcao</t>
+          <t>ameacas</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>defesa_civil</t>
+          <t>observacao_ao_longo_dos_anos</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Defesa Civil</t>
+          <t>Observação ao longo dos anos</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>dados_meteorologicos</t>
+          <t>relatos_de_moradores_antigos</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Dados meteorológicos (ex.: INMET)</t>
+          <t>Relatos de moradores antigos</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>universidade</t>
+          <t>comparacao_com_registros</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Universidade</t>
+          <t>Comparação com registros</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>ong</t>
+          <t>noticias</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>Notícias</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>fontes_risco</t>
+          <t>base_percepcao</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>conhecimento_tradicional</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Conhecimento tradicional</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -22846,12 +22886,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>nao_ha_fonte_consultada</t>
+          <t>defesa_civil</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Não há fonte consultada</t>
+          <t>Defesa Civil</t>
         </is>
       </c>
     </row>
@@ -22863,172 +22903,172 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>dados_meteorologicos</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Dados meteorológicos (ex.: INMET)</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>afetou</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>escola</t>
+          <t>universidade</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Universidade</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>afetou</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>ong</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>ONG</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>afetou</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>ambos</t>
+          <t>conhecimento_tradicional</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Ambos</t>
+          <t>Conhecimento tradicional</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>afetou</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>nenhum</t>
+          <t>nao_ha_fonte_consultada</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>Não há fonte consultada</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>afetou</t>
+          <t>fontes_risco</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>afetou</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>raro</t>
+          <t>escola</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Raro (já ocorreu uma vez)</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>afetou</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>ocasional</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Ocasional</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>afetou</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>frequente</t>
+          <t>ambos</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Frequente</t>
+          <t>Ambos</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>afetou</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>muito_frequente_recorrente</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Muito frequente/recorrente</t>
+          <t>Nenhum</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>freq_risco</t>
+          <t>afetou</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -23045,85 +23085,85 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>impacto_risco</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>interrupcao_de_aulas</t>
+          <t>raro</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Interrupção de aulas</t>
+          <t>Raro (já ocorreu uma vez)</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>impacto_risco</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>danos_a_estrutura</t>
+          <t>ocasional</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Danos à estrutura</t>
+          <t>Ocasional</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>impacto_risco</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>acesso_interrompido</t>
+          <t>frequente</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Acesso interrompido</t>
+          <t>Frequente</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>impacto_risco</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>perda_de_materiais</t>
+          <t>muito_frequente_recorrente</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Perda de materiais</t>
+          <t>Muito frequente/recorrente</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>impacto_risco</t>
+          <t>freq_risco</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>impacto_na_saude</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Impacto na saúde</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -23135,12 +23175,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>impacto_emocional</t>
+          <t>interrupcao_de_aulas</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Impacto emocional</t>
+          <t>Interrupção de aulas</t>
         </is>
       </c>
     </row>
@@ -23152,97 +23192,97 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>danos_a_estrutura</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Danos à estrutura</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>ativos</t>
+          <t>impacto_risco</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>predio_escolar</t>
+          <t>acesso_interrompido</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Prédio escolar</t>
+          <t>Acesso interrompido</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>ativos</t>
+          <t>impacto_risco</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>biblioteca</t>
+          <t>perda_de_materiais</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Biblioteca</t>
+          <t>Perda de materiais</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>ativos</t>
+          <t>impacto_risco</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>quadra</t>
+          <t>impacto_na_saude</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Quadra</t>
+          <t>Impacto na saúde</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ativos</t>
+          <t>impacto_risco</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>horta</t>
+          <t>impacto_emocional</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Horta</t>
+          <t>Impacto emocional</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>ativos</t>
+          <t>impacto_risco</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>equipamentos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Equipamentos</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23254,12 +23294,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>arquivos_documentos</t>
+          <t>predio_escolar</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Arquivos/documentos</t>
+          <t>Prédio escolar</t>
         </is>
       </c>
     </row>
@@ -23271,97 +23311,97 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>biblioteca</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Biblioteca</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>grupos_exp</t>
+          <t>ativos</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>quadra</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Quadra</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>grupos_exp</t>
+          <t>ativos</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>horta</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Horta</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>grupos_exp</t>
+          <t>ativos</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>equipamentos</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Equipamentos</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>grupos_exp</t>
+          <t>ativos</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>arquivos_documentos</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Arquivos/documentos</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>grupos_exp</t>
+          <t>ativos</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>pessoas_com_deficiencia</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Pessoas com deficiência</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23373,12 +23413,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>criancas_pequenas</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Crianças pequenas</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -23390,12 +23430,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>idosos</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Idosos</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
@@ -23407,97 +23447,97 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>grupos_exp</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>acessibilidade_limitada_nas_rota</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Acessibilidade limitada nas rotas de saída</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>grupos_exp</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>ausencia_de_sinalizacao_de_emerg</t>
+          <t>pessoas_com_deficiencia</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Ausência de sinalização de emergência</t>
+          <t>Pessoas com deficiência</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>grupos_exp</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>estrutura_fisica_fragilizada</t>
+          <t>criancas_pequenas</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Estrutura física fragilizada</t>
+          <t>Crianças pequenas</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>grupos_exp</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>ausencia_de_comunicacao_acessive</t>
+          <t>idosos</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Ausência de comunicação acessível (Libras/Braile/linguagem simples)</t>
+          <t>Idosos</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>cond_amplia</t>
+          <t>grupos_exp</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>ausencia_de_plano_de_evacuacao_a</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Ausência de plano de evacuação adaptado</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -23509,12 +23549,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>distancia_de_pontos_de_apoio_soc</t>
+          <t>acessibilidade_limitada_nas_rota</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Distância de pontos de apoio/socorro</t>
+          <t>Acessibilidade limitada nas rotas de saída</t>
         </is>
       </c>
     </row>
@@ -23526,97 +23566,97 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>ausencia_de_sinalizacao_de_emerg</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Outra condição</t>
+          <t>Ausência de sinalização de emergência</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>brigada_equipe_treinada</t>
+          <t>estrutura_fisica_fragilizada</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Brigada/equipe treinada</t>
+          <t>Estrutura física fragilizada</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>plano_de_evacuacao</t>
+          <t>ausencia_de_comunicacao_acessive</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Plano de evacuação</t>
+          <t>Ausência de comunicação acessível (Libras/Braile/linguagem simples)</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>comunicacao_de_alerta</t>
+          <t>ausencia_de_plano_de_evacuacao_a</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Comunicação de alerta</t>
+          <t>Ausência de plano de evacuação adaptado</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>apoio_de_rede_externa</t>
+          <t>distancia_de_pontos_de_apoio_soc</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Apoio de rede externa</t>
+          <t>Distância de pontos de apoio/socorro</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>cap_resp</t>
+          <t>cond_amplia</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>kit_de_emergencia</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Kit de emergência</t>
+          <t>Outra condição</t>
         </is>
       </c>
     </row>
@@ -23628,12 +23668,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>nenhuma_identificada</t>
+          <t>brigada_equipe_treinada</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Nenhuma identificada</t>
+          <t>Brigada/equipe treinada</t>
         </is>
       </c>
     </row>
@@ -23645,478 +23685,478 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>plano_de_evacuacao</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Plano de evacuação</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>boa</t>
+          <t>comunicacao_de_alerta</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Comunicação de alerta</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>apoio_de_rede_externa</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Apoio de rede externa</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>fraca</t>
+          <t>kit_de_emergencia</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Fraca</t>
+          <t>Kit de emergência</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>inexistente</t>
+          <t>nenhuma_identificada</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Inexistente</t>
+          <t>Nenhuma identificada</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>aval_cap</t>
+          <t>cap_resp</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>boa</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>fraca</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Fraca</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>bma_ns</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Inexistente</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>aval_cap</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>bma</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>1 — Muito baixa</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma_ns</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>3 — Média</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>prio_1a5</t>
+          <t>bma</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>5 — Muito alta</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>marc_risco</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>lacuna</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Não sabemos avaliar isso com segurança (gera lacuna de conhecimento)</t>
+          <t>1 — Muito baixa</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>marc_risco</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>aval_externa</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Requer avaliação técnica externa</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>marc_risco</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>selecionado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Selecionar este risco para a Leitura Integrada e planejamento</t>
+          <t>3 — Média</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>cartog_quem</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>cartog_quem</t>
+          <t>prio_1a5</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>5 — Muito alta</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>cartog_quem</t>
+          <t>marc_risco</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>lacuna</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Não sabemos avaliar isso com segurança (gera lacuna de conhecimento)</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>cartog_quem</t>
+          <t>marc_risco</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>aval_externa</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Requer avaliação técnica externa</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>marc_risco</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>individual</t>
+          <t>selecionado</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Selecionar este risco para a Leitura Integrada e planejamento</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>cartog_quem</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>uma_turma</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Uma turma</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>cartog_quem</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>toda_a_escola</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Todo o local</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>cartog_quem</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -24133,170 +24173,170 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>abrangencia</t>
+          <t>cartog_quem</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>territorio</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Território</t>
+          <t>Outros</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>a_escola_pode_agir_sozinha</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>O local pode agir sozinho</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>precisa_de_parceria</t>
+          <t>uma_turma</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Precisa de parceria</t>
+          <t>Uma turma</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>esta_fora_do_alcance_da_escola</t>
+          <t>toda_a_escola</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Está fora do alcance do local</t>
+          <t>Todo o local</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>acionavel</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>nao_sabe</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Não sabe</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>abrangencia</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>territorio</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Território</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>a_escola_pode_agir_sozinha</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>O local pode agir sozinho</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>funcionarios</t>
+          <t>precisa_de_parceria</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Funcionários(as)</t>
+          <t>Precisa de parceria</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>esta_fora_do_alcance_da_escola</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Está fora do alcance do local</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>afetados</t>
+          <t>acionavel</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>nao_sabe</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Não sabe</t>
         </is>
       </c>
     </row>
@@ -24308,97 +24348,97 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>funcionarios</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Funcionários(as)</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>decisao_part</t>
+          <t>afetados</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24410,12 +24450,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>conselho_escolar</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Conselho escolar</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
@@ -24427,97 +24467,97 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>votacao</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Votação</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>consenso</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Consenso</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>decisao_da_gestao</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Decisão da gestão</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>criterios_tecnicos</t>
+          <t>conselho_escolar</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Critérios técnicos</t>
+          <t>Conselho escolar</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>metodo_sel</t>
+          <t>decisao_part</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>discussao_coletiva</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Discussão coletiva</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24529,97 +24569,97 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>votacao</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Votação</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>acao_estrutural</t>
+          <t>consenso</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Ação estrutural</t>
+          <t>Consenso</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>acao_pedagogica</t>
+          <t>decisao_da_gestao</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Ação pedagógica</t>
+          <t>Decisão da gestão</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>articulacao_institucional</t>
+          <t>criterios_tecnicos</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Articulação institucional</t>
+          <t>Critérios técnicos</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>comunicacao</t>
+          <t>discussao_coletiva</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Comunicação</t>
+          <t>Discussão coletiva</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>resp_tipo</t>
+          <t>metodo_sel</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>mobilizacao_comunitaria</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Mobilização comunitária</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -24631,12 +24671,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>monitoramento</t>
+          <t>acao_estrutural</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Monitoramento</t>
+          <t>Ação estrutural</t>
         </is>
       </c>
     </row>
@@ -24648,165 +24688,165 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>acao_pedagogica</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Ação pedagógica</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>planejada</t>
+          <t>articulacao_institucional</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Planejada</t>
+          <t>Articulação institucional</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>em_andamento</t>
+          <t>comunicacao</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Comunicação</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>concluida</t>
+          <t>mobilizacao_comunitaria</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Mobilização comunitária</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>status_ativ</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>nao_realizada</t>
+          <t>monitoramento</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Não realizada</t>
+          <t>Monitoramento</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>resp_tipo</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>planejada</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Planejada</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>em_andamento</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Em andamento</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>concluida</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>publicos</t>
+          <t>status_ativ</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>gestao</t>
+          <t>nao_realizada</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Gestão</t>
+          <t>Não realizada</t>
         </is>
       </c>
     </row>
@@ -24818,233 +24858,233 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>espectador</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Espectador</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>participante</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Participante</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>protagonista</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Protagonista</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>papel_estud2</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>coprodutor</t>
+          <t>gestao</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Coprodutor</t>
+          <t>Gestão</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>publicos</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>espectador</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Espectador</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>participante</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Baixa</t>
+          <t>Participante</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>viabilidade</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>incerta</t>
+          <t>protagonista</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Incerta</t>
+          <t>Protagonista</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>papel_estud2</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>aprovacao_da_gestao</t>
+          <t>coprodutor</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Aprovação da gestão</t>
+          <t>Coprodutor</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>recursos_financeiros</t>
+          <t>alta</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Recursos financeiros</t>
+          <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>parceria_externa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Parceria externa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>formacao_previa</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Formação prévia</t>
+          <t>Baixa</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>dependencias</t>
+          <t>viabilidade</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>incerta</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Incerta</t>
         </is>
       </c>
     </row>
@@ -25056,97 +25096,97 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>aprovacao_da_gestao</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Aprovação da gestão</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>fotos</t>
+          <t>recursos_financeiros</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Fotos</t>
+          <t>Recursos financeiros</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>lista_de_presenca</t>
+          <t>parceria_externa</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Lista de presença</t>
+          <t>Parceria externa</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>producao_dos_estudantes</t>
+          <t>formacao_previa</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Produção dos estudantes</t>
+          <t>Formação prévia</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>registro_em_ata</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Registro em ata</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>evid_exec</t>
+          <t>dependencias</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>depoimentos</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Depoimentos</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
@@ -25158,97 +25198,97 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>fotos</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Fotos</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>tempo</t>
+          <t>lista_de_presenca</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Lista de presença</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>recursos</t>
+          <t>producao_dos_estudantes</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Recursos</t>
+          <t>Produção dos estudantes</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>articulacao</t>
+          <t>registro_em_ata</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Articulação</t>
+          <t>Registro em ata</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>depoimentos</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Clima</t>
+          <t>Depoimentos</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>barr_impl</t>
+          <t>evid_exec</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>adesao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Adesão</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -25260,148 +25300,148 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>tempo</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Tempo</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>coerente</t>
+          <t>recursos</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Coerente</t>
+          <t>Recursos</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>parcialmente_coerente</t>
+          <t>articulacao</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Parcialmente coerente</t>
+          <t>Articulação</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>coerencia</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>nao_tenho_certeza</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Não tenho certeza</t>
+          <t>Clima</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>informar</t>
+          <t>adesao</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Informar</t>
+          <t>Adesão</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>barr_impl</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>sensibilizar</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Sensibilizar</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>coerencia</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>mobilizar</t>
+          <t>coerente</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Mobilizar</t>
+          <t>Coerente</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>coerencia</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>prestar_contas</t>
+          <t>parcialmente_coerente</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Prestar contas</t>
+          <t>Parcialmente coerente</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>com_final</t>
+          <t>coerencia</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>dar_voz_a_comunidade</t>
+          <t>nao_tenho_certeza</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Dar voz à comunidade</t>
+          <t>Não tenho certeza</t>
         </is>
       </c>
     </row>
@@ -25413,97 +25453,97 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>informar</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Informar</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>sensibilizar</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Sensibilizar</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>mobilizar</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Mobilizar</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>familias</t>
+          <t>prestar_contas</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Prestar contas</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>comunidade</t>
+          <t>dar_voz_a_comunidade</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Comunidade</t>
+          <t>Dar voz à comunidade</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>com_publico</t>
+          <t>com_final</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>poder_publico</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Poder público</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -25515,97 +25555,97 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>caixa_de_sugestoes</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Caixa de sugestões</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>roda_de_conversa</t>
+          <t>familias</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Roda de conversa</t>
+          <t>Famílias</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>formulario</t>
+          <t>comunidade</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Formulário</t>
+          <t>Comunidade</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>poder_publico</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Poder público</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>com_escuta</t>
+          <t>com_publico</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>reuniao</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Reunião</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -25617,97 +25657,97 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>caixa_de_sugestoes</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Caixa de sugestões</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>cartaz</t>
+          <t>roda_de_conversa</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Cartaz</t>
+          <t>Roda de conversa</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>radio_escolar</t>
+          <t>formulario</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Rádio escolar</t>
+          <t>Formulário</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>redes_sociais</t>
+          <t>reuniao</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Redes sociais</t>
+          <t>Reunião</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>com_midia</t>
+          <t>com_escuta</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>jornal_mural</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Jornal mural</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
@@ -25719,12 +25759,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>teatro</t>
+          <t>cartaz</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Teatro</t>
+          <t>Cartaz</t>
         </is>
       </c>
     </row>
@@ -25736,12 +25776,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>podcast</t>
+          <t>radio_escolar</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Podcast</t>
+          <t>Rádio escolar</t>
         </is>
       </c>
     </row>
@@ -25753,87 +25793,87 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>outro</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Vídeo</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>idioma_linguagem_tecnica</t>
+          <t>redes_sociais</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Idioma/linguagem técnica</t>
+          <t>Redes sociais</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>acessibilidade_para_pessoas_com_</t>
+          <t>jornal_mural</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Acessibilidade para pessoas com deficiência</t>
+          <t>Jornal mural</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>falta_de_conectividade</t>
+          <t>teatro</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Falta de conectividade</t>
+          <t>Teatro</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>alfabetizacao</t>
+          <t>podcast</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Alfabetização</t>
+          <t>Podcast</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>com_barr</t>
+          <t>com_midia</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -25843,82 +25883,82 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>estudantes</t>
+          <t>idioma_linguagem_tecnica</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Estudantes</t>
+          <t>Idioma/linguagem técnica</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>professores</t>
+          <t>acessibilidade_para_pessoas_com_</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Professores(as)</t>
+          <t>Acessibilidade para pessoas com deficiência</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>comunicacao_escolar</t>
+          <t>falta_de_conectividade</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Comunicação escolar</t>
+          <t>Falta de conectividade</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>parceiros_externos</t>
+          <t>alfabetizacao</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Parceiros externos</t>
+          <t>Alfabetização</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>com_produz</t>
+          <t>com_barr</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -25928,211 +25968,211 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Outro</t>
+          <t>Outra</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>nenhuma</t>
+          <t>estudantes</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Nenhuma</t>
+          <t>Estudantes</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>sao_consultados</t>
+          <t>professores</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>São consultados</t>
+          <t>Professores(as)</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>colaboram_na_producao</t>
+          <t>comunicacao_escolar</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Colaboram na produção</t>
+          <t>Comunicação escolar</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>com_decisao</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>decidem_conteudo_formato</t>
+          <t>parceiros_externos</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Decidem conteúdo/formato</t>
+          <t>Parceiros externos</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_produz</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>processo</t>
+          <t>outro</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Processo</t>
+          <t>Outro</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>participacao</t>
+          <t>nenhuma</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Participação</t>
+          <t>Nenhuma</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>ind_tipo</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>sao_consultados</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>São consultados</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>mensal</t>
+          <t>colaboram_na_producao</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Mensal</t>
+          <t>Colaboram na produção</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>com_decisao</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>bimestral</t>
+          <t>decidem_conteudo_formato</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Bimestral</t>
+          <t>Decidem conteúdo/formato</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>trimestral</t>
+          <t>processo</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Processo</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>semestral</t>
+          <t>participacao</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Semestral</t>
+          <t>Participação</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>periodicidade</t>
+          <t>ind_tipo</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>anual</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Anual</t>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
@@ -26144,10 +26184,95 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>bimestral</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>trimestral</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>semestral</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>periodicidade</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
           <t>por_evento</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr">
+      <c r="C681" t="inlineStr">
         <is>
           <t>Por evento</t>
         </is>
